--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98006</v>
+        <v>98009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98009</v>
+        <v>98010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98010</v>
+        <v>98015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136615192</v>
       </c>
       <c r="B3" t="n">
-        <v>58019</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136615201</v>
       </c>
       <c r="B4" t="n">
-        <v>58019</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136615158</v>
       </c>
       <c r="B5" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136615160</v>
       </c>
       <c r="B6" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136615198</v>
       </c>
       <c r="B7" t="n">
-        <v>58665</v>
+        <v>58667</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98015</v>
+        <v>98017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98017</v>
+        <v>98023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98023</v>
+        <v>98025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98025</v>
+        <v>98026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98026</v>
+        <v>98032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98032</v>
+        <v>98036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98036</v>
+        <v>98038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98038</v>
+        <v>98040</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98040</v>
+        <v>98053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136615192</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136615201</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136615158</v>
       </c>
       <c r="B5" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136615160</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136615198</v>
       </c>
       <c r="B7" t="n">
-        <v>58667</v>
+        <v>58680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4263-2024 artfynd.xlsx
+++ b/artfynd/A 4263-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136615791</v>
       </c>
       <c r="B2" t="n">
-        <v>98053</v>
+        <v>98055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136615192</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136615201</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>136615158</v>
       </c>
       <c r="B5" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136615160</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136615198</v>
       </c>
       <c r="B7" t="n">
-        <v>58680</v>
+        <v>58682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
